--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128494331</v>
       </c>
       <c r="B2" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128494318</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128494315</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128494325</v>
+        <v>128494311</v>
       </c>
       <c r="B5" t="n">
-        <v>80136</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519838</v>
+        <v>520007</v>
       </c>
       <c r="R5" t="n">
-        <v>7145721</v>
+        <v>7145630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494311</v>
+        <v>128494313</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,7 +1116,7 @@
         <v>520007</v>
       </c>
       <c r="R6" t="n">
-        <v>7145630</v>
+        <v>7145627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494313</v>
+        <v>128494325</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>80189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520007</v>
+        <v>519838</v>
       </c>
       <c r="R7" t="n">
-        <v>7145627</v>
+        <v>7145721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494307</v>
+        <v>128494330</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>80188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520304</v>
+        <v>519865</v>
       </c>
       <c r="R8" t="n">
-        <v>7145224</v>
+        <v>7145612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494317</v>
+        <v>128494327</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>80189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520006</v>
+        <v>520435</v>
       </c>
       <c r="R9" t="n">
-        <v>7145617</v>
+        <v>7145468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494327</v>
+        <v>128494307</v>
       </c>
       <c r="B10" t="n">
-        <v>80136</v>
+        <v>57685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520435</v>
+        <v>520304</v>
       </c>
       <c r="R10" t="n">
-        <v>7145468</v>
+        <v>7145224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,6 +1542,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494314</v>
+        <v>128494317</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520005</v>
+        <v>520006</v>
       </c>
       <c r="R11" t="n">
-        <v>7145625</v>
+        <v>7145617</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,27 +1675,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494333</v>
+        <v>128494314</v>
       </c>
       <c r="B12" t="n">
-        <v>57777</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520038</v>
+        <v>520005</v>
       </c>
       <c r="R12" t="n">
-        <v>7145570</v>
+        <v>7145625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1746,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494330</v>
+        <v>128494333</v>
       </c>
       <c r="B13" t="n">
-        <v>80135</v>
+        <v>57789</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519865</v>
+        <v>520038</v>
       </c>
       <c r="R13" t="n">
-        <v>7145612</v>
+        <v>7145570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
         <v>128494316</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128494322</v>
+        <v>128494310</v>
       </c>
       <c r="B15" t="n">
-        <v>57670</v>
+        <v>57685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,16 +1987,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520419</v>
+        <v>520004</v>
       </c>
       <c r="R15" t="n">
-        <v>7145725</v>
+        <v>7145632</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128494310</v>
+        <v>128494322</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>57682</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520004</v>
+        <v>520419</v>
       </c>
       <c r="R16" t="n">
-        <v>7145632</v>
+        <v>7145725</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2183,7 +2183,7 @@
         <v>128494312</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128494305</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128494319</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>128494308</v>
       </c>
       <c r="B20" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,32 +2588,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494332</v>
+        <v>128494328</v>
       </c>
       <c r="B21" t="n">
-        <v>80135</v>
+        <v>97454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520316</v>
+        <v>520407</v>
       </c>
       <c r="R21" t="n">
-        <v>7145323</v>
+        <v>7145701</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,32 +2685,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128494328</v>
+        <v>128494332</v>
       </c>
       <c r="B22" t="n">
-        <v>97361</v>
+        <v>80188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520407</v>
+        <v>520316</v>
       </c>
       <c r="R22" t="n">
-        <v>7145701</v>
+        <v>7145323</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
         <v>128494324</v>
       </c>
       <c r="B23" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>128494309</v>
       </c>
       <c r="B24" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>128494320</v>
       </c>
       <c r="B25" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>128494323</v>
       </c>
       <c r="B26" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>128494321</v>
       </c>
       <c r="B27" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128494315</v>
+        <v>128494325</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>80189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520004</v>
+        <v>519838</v>
       </c>
       <c r="R4" t="n">
-        <v>7145622</v>
+        <v>7145721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128494311</v>
+        <v>128494315</v>
       </c>
       <c r="B5" t="n">
         <v>57685</v>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520007</v>
+        <v>520004</v>
       </c>
       <c r="R5" t="n">
-        <v>7145630</v>
+        <v>7145622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494313</v>
+        <v>128494311</v>
       </c>
       <c r="B6" t="n">
         <v>57685</v>
@@ -1116,7 +1111,7 @@
         <v>520007</v>
       </c>
       <c r="R6" t="n">
-        <v>7145627</v>
+        <v>7145630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494325</v>
+        <v>128494313</v>
       </c>
       <c r="B7" t="n">
-        <v>80189</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519838</v>
+        <v>520007</v>
       </c>
       <c r="R7" t="n">
-        <v>7145721</v>
+        <v>7145627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494330</v>
+        <v>128494327</v>
       </c>
       <c r="B8" t="n">
-        <v>80188</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519865</v>
+        <v>520435</v>
       </c>
       <c r="R8" t="n">
-        <v>7145612</v>
+        <v>7145468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494327</v>
+        <v>128494330</v>
       </c>
       <c r="B9" t="n">
-        <v>80189</v>
+        <v>80188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520435</v>
+        <v>519865</v>
       </c>
       <c r="R9" t="n">
-        <v>7145468</v>
+        <v>7145612</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128494332</v>
+        <v>128494324</v>
       </c>
       <c r="B22" t="n">
-        <v>80188</v>
+        <v>80189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520316</v>
+        <v>519826</v>
       </c>
       <c r="R22" t="n">
-        <v>7145323</v>
+        <v>7145720</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128494324</v>
+        <v>128494332</v>
       </c>
       <c r="B23" t="n">
-        <v>80189</v>
+        <v>80188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2793,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519826</v>
+        <v>520316</v>
       </c>
       <c r="R23" t="n">
-        <v>7145720</v>
+        <v>7145323</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494327</v>
+        <v>128494333</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>57789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520435</v>
+        <v>520038</v>
       </c>
       <c r="R8" t="n">
-        <v>7145468</v>
+        <v>7145570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494330</v>
+        <v>128494327</v>
       </c>
       <c r="B9" t="n">
-        <v>80188</v>
+        <v>80189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519865</v>
+        <v>520435</v>
       </c>
       <c r="R9" t="n">
-        <v>7145612</v>
+        <v>7145468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494333</v>
+        <v>128494330</v>
       </c>
       <c r="B13" t="n">
-        <v>57789</v>
+        <v>80188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520038</v>
+        <v>519865</v>
       </c>
       <c r="R13" t="n">
-        <v>7145570</v>
+        <v>7145612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2588,32 +2588,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494328</v>
+        <v>128494324</v>
       </c>
       <c r="B21" t="n">
-        <v>97454</v>
+        <v>80189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520407</v>
+        <v>519826</v>
       </c>
       <c r="R21" t="n">
-        <v>7145701</v>
+        <v>7145720</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128494324</v>
+        <v>128494332</v>
       </c>
       <c r="B22" t="n">
-        <v>80189</v>
+        <v>80188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519826</v>
+        <v>520316</v>
       </c>
       <c r="R22" t="n">
-        <v>7145720</v>
+        <v>7145323</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,32 +2782,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128494332</v>
+        <v>128494328</v>
       </c>
       <c r="B23" t="n">
-        <v>80188</v>
+        <v>97454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520316</v>
+        <v>520407</v>
       </c>
       <c r="R23" t="n">
-        <v>7145323</v>
+        <v>7145701</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128494331</v>
       </c>
       <c r="B2" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128494318</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128494325</v>
+        <v>128494315</v>
       </c>
       <c r="B4" t="n">
-        <v>80189</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519838</v>
+        <v>520004</v>
       </c>
       <c r="R4" t="n">
-        <v>7145721</v>
+        <v>7145622</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128494315</v>
+        <v>128494311</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520004</v>
+        <v>520007</v>
       </c>
       <c r="R5" t="n">
-        <v>7145622</v>
+        <v>7145630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494311</v>
+        <v>128494313</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,7 +1116,7 @@
         <v>520007</v>
       </c>
       <c r="R6" t="n">
-        <v>7145630</v>
+        <v>7145627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494313</v>
+        <v>128494325</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>80193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520007</v>
+        <v>519838</v>
       </c>
       <c r="R7" t="n">
-        <v>7145627</v>
+        <v>7145721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494333</v>
+        <v>128494327</v>
       </c>
       <c r="B8" t="n">
-        <v>57789</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520038</v>
+        <v>520435</v>
       </c>
       <c r="R8" t="n">
-        <v>7145570</v>
+        <v>7145468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494327</v>
+        <v>128494330</v>
       </c>
       <c r="B9" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520435</v>
+        <v>519865</v>
       </c>
       <c r="R9" t="n">
-        <v>7145468</v>
+        <v>7145612</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,27 +1471,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494307</v>
+        <v>128494333</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>57793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520304</v>
+        <v>520038</v>
       </c>
       <c r="R10" t="n">
-        <v>7145224</v>
+        <v>7145570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494317</v>
+        <v>128494307</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520006</v>
+        <v>520304</v>
       </c>
       <c r="R11" t="n">
-        <v>7145617</v>
+        <v>7145224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1643,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494314</v>
+        <v>128494317</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520005</v>
+        <v>520006</v>
       </c>
       <c r="R12" t="n">
-        <v>7145625</v>
+        <v>7145617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494330</v>
+        <v>128494314</v>
       </c>
       <c r="B13" t="n">
-        <v>80188</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519865</v>
+        <v>520005</v>
       </c>
       <c r="R13" t="n">
-        <v>7145612</v>
+        <v>7145625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,6 +1843,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1877,7 +1877,7 @@
         <v>128494316</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>128494310</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>128494322</v>
       </c>
       <c r="B16" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128494312</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128494305</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128494319</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>128494308</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>128494324</v>
       </c>
       <c r="B21" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>128494332</v>
       </c>
       <c r="B22" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>128494328</v>
       </c>
       <c r="B23" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>128494309</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>128494320</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>128494323</v>
       </c>
       <c r="B26" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>128494321</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128494315</v>
+        <v>128494325</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>80193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520004</v>
+        <v>519838</v>
       </c>
       <c r="R4" t="n">
-        <v>7145622</v>
+        <v>7145721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128494311</v>
+        <v>128494315</v>
       </c>
       <c r="B5" t="n">
         <v>57689</v>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520007</v>
+        <v>520004</v>
       </c>
       <c r="R5" t="n">
-        <v>7145630</v>
+        <v>7145622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494313</v>
+        <v>128494311</v>
       </c>
       <c r="B6" t="n">
         <v>57689</v>
@@ -1116,7 +1111,7 @@
         <v>520007</v>
       </c>
       <c r="R6" t="n">
-        <v>7145627</v>
+        <v>7145630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494325</v>
+        <v>128494313</v>
       </c>
       <c r="B7" t="n">
-        <v>80193</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519838</v>
+        <v>520007</v>
       </c>
       <c r="R7" t="n">
-        <v>7145721</v>
+        <v>7145627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494330</v>
+        <v>128494307</v>
       </c>
       <c r="B9" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519865</v>
+        <v>520304</v>
       </c>
       <c r="R9" t="n">
-        <v>7145612</v>
+        <v>7145224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1445,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,27 +1476,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494333</v>
+        <v>128494317</v>
       </c>
       <c r="B10" t="n">
-        <v>57793</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520038</v>
+        <v>520006</v>
       </c>
       <c r="R10" t="n">
-        <v>7145570</v>
+        <v>7145617</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494307</v>
+        <v>128494314</v>
       </c>
       <c r="B11" t="n">
         <v>57689</v>
@@ -1603,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520304</v>
+        <v>520005</v>
       </c>
       <c r="R11" t="n">
-        <v>7145224</v>
+        <v>7145625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,27 +1680,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494317</v>
+        <v>128494333</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>57793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1705,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520006</v>
+        <v>520038</v>
       </c>
       <c r="R12" t="n">
-        <v>7145617</v>
+        <v>7145570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494314</v>
+        <v>128494330</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>80192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520005</v>
+        <v>519865</v>
       </c>
       <c r="R13" t="n">
-        <v>7145625</v>
+        <v>7145612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,11 +1848,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494324</v>
+        <v>128494332</v>
       </c>
       <c r="B21" t="n">
-        <v>80193</v>
+        <v>80192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519826</v>
+        <v>520316</v>
       </c>
       <c r="R21" t="n">
-        <v>7145720</v>
+        <v>7145323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128494332</v>
+        <v>128494324</v>
       </c>
       <c r="B22" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520316</v>
+        <v>519826</v>
       </c>
       <c r="R22" t="n">
-        <v>7145323</v>
+        <v>7145720</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
         <v>128494328</v>
       </c>
       <c r="B23" t="n">
-        <v>97460</v>
+        <v>97466</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494307</v>
+        <v>128494330</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>80192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520304</v>
+        <v>519865</v>
       </c>
       <c r="R9" t="n">
-        <v>7145224</v>
+        <v>7145612</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494317</v>
+        <v>128494307</v>
       </c>
       <c r="B10" t="n">
         <v>57689</v>
@@ -1511,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520006</v>
+        <v>520304</v>
       </c>
       <c r="R10" t="n">
-        <v>7145617</v>
+        <v>7145224</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1546,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,7 +1573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494314</v>
+        <v>128494317</v>
       </c>
       <c r="B11" t="n">
         <v>57689</v>
@@ -1613,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520005</v>
+        <v>520006</v>
       </c>
       <c r="R11" t="n">
-        <v>7145625</v>
+        <v>7145617</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,27 +1675,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494333</v>
+        <v>128494314</v>
       </c>
       <c r="B12" t="n">
-        <v>57793</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520038</v>
+        <v>520005</v>
       </c>
       <c r="R12" t="n">
-        <v>7145570</v>
+        <v>7145625</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1746,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494330</v>
+        <v>128494333</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>57793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519865</v>
+        <v>520038</v>
       </c>
       <c r="R13" t="n">
-        <v>7145612</v>
+        <v>7145570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494332</v>
+        <v>128494324</v>
       </c>
       <c r="B21" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520316</v>
+        <v>519826</v>
       </c>
       <c r="R21" t="n">
-        <v>7145323</v>
+        <v>7145720</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128494324</v>
+        <v>128494332</v>
       </c>
       <c r="B22" t="n">
-        <v>80193</v>
+        <v>80192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519826</v>
+        <v>520316</v>
       </c>
       <c r="R22" t="n">
-        <v>7145720</v>
+        <v>7145323</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128494331</v>
       </c>
       <c r="B2" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128494325</v>
+        <v>128494313</v>
       </c>
       <c r="B4" t="n">
-        <v>80193</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519838</v>
+        <v>520007</v>
       </c>
       <c r="R4" t="n">
-        <v>7145721</v>
+        <v>7145627</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128494315</v>
+        <v>128494325</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>80195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520004</v>
+        <v>519838</v>
       </c>
       <c r="R5" t="n">
-        <v>7145622</v>
+        <v>7145721</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494311</v>
+        <v>128494315</v>
       </c>
       <c r="B6" t="n">
         <v>57689</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520007</v>
+        <v>520004</v>
       </c>
       <c r="R6" t="n">
-        <v>7145630</v>
+        <v>7145622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494313</v>
+        <v>128494311</v>
       </c>
       <c r="B7" t="n">
         <v>57689</v>
@@ -1213,7 +1213,7 @@
         <v>520007</v>
       </c>
       <c r="R7" t="n">
-        <v>7145627</v>
+        <v>7145630</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494327</v>
+        <v>128494307</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520435</v>
+        <v>520304</v>
       </c>
       <c r="R8" t="n">
-        <v>7145468</v>
+        <v>7145224</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494330</v>
+        <v>128494317</v>
       </c>
       <c r="B9" t="n">
-        <v>80192</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519865</v>
+        <v>520006</v>
       </c>
       <c r="R9" t="n">
-        <v>7145612</v>
+        <v>7145617</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1450,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494307</v>
+        <v>128494314</v>
       </c>
       <c r="B10" t="n">
         <v>57689</v>
@@ -1506,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520304</v>
+        <v>520005</v>
       </c>
       <c r="R10" t="n">
-        <v>7145224</v>
+        <v>7145625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494317</v>
+        <v>128494327</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>80195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520006</v>
+        <v>520435</v>
       </c>
       <c r="R11" t="n">
-        <v>7145617</v>
+        <v>7145468</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494314</v>
+        <v>128494330</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520005</v>
+        <v>519865</v>
       </c>
       <c r="R12" t="n">
-        <v>7145625</v>
+        <v>7145612</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2591,7 +2591,7 @@
         <v>128494324</v>
       </c>
       <c r="B21" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>128494332</v>
       </c>
       <c r="B22" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>128494328</v>
       </c>
       <c r="B23" t="n">
-        <v>97466</v>
+        <v>97468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128494313</v>
+        <v>128494325</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>80195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520007</v>
+        <v>519838</v>
       </c>
       <c r="R4" t="n">
-        <v>7145627</v>
+        <v>7145721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128494325</v>
+        <v>128494315</v>
       </c>
       <c r="B5" t="n">
-        <v>80195</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519838</v>
+        <v>520004</v>
       </c>
       <c r="R5" t="n">
-        <v>7145721</v>
+        <v>7145622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494315</v>
+        <v>128494311</v>
       </c>
       <c r="B6" t="n">
         <v>57689</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520004</v>
+        <v>520007</v>
       </c>
       <c r="R6" t="n">
-        <v>7145622</v>
+        <v>7145630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494311</v>
+        <v>128494313</v>
       </c>
       <c r="B7" t="n">
         <v>57689</v>
@@ -1213,7 +1213,7 @@
         <v>520007</v>
       </c>
       <c r="R7" t="n">
-        <v>7145630</v>
+        <v>7145627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494307</v>
+        <v>128494327</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>80195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520304</v>
+        <v>520435</v>
       </c>
       <c r="R8" t="n">
-        <v>7145224</v>
+        <v>7145468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,27 +1374,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494317</v>
+        <v>128494333</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1414,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520006</v>
+        <v>520038</v>
       </c>
       <c r="R9" t="n">
-        <v>7145617</v>
+        <v>7145570</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494314</v>
+        <v>128494330</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>80194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520005</v>
+        <v>519865</v>
       </c>
       <c r="R10" t="n">
-        <v>7145625</v>
+        <v>7145612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494327</v>
+        <v>128494307</v>
       </c>
       <c r="B11" t="n">
-        <v>80195</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520435</v>
+        <v>520304</v>
       </c>
       <c r="R11" t="n">
-        <v>7145468</v>
+        <v>7145224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1639,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494330</v>
+        <v>128494317</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519865</v>
+        <v>520006</v>
       </c>
       <c r="R12" t="n">
-        <v>7145612</v>
+        <v>7145617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1741,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,27 +1772,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494333</v>
+        <v>128494314</v>
       </c>
       <c r="B13" t="n">
-        <v>57793</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1812,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520038</v>
+        <v>520005</v>
       </c>
       <c r="R13" t="n">
-        <v>7145570</v>
+        <v>7145625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,6 +1843,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128494316</v>
+        <v>128494322</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,16 +1885,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520004</v>
+        <v>520419</v>
       </c>
       <c r="R14" t="n">
-        <v>7145617</v>
+        <v>7145725</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128494310</v>
+        <v>128494316</v>
       </c>
       <c r="B15" t="n">
         <v>57689</v>
@@ -2014,7 +2014,7 @@
         <v>520004</v>
       </c>
       <c r="R15" t="n">
-        <v>7145632</v>
+        <v>7145617</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128494322</v>
+        <v>128494310</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520419</v>
+        <v>520004</v>
       </c>
       <c r="R16" t="n">
-        <v>7145725</v>
+        <v>7145632</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2180,7 +2180,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128494312</v>
+        <v>128494305</v>
       </c>
       <c r="B17" t="n">
         <v>57689</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520006</v>
+        <v>519885</v>
       </c>
       <c r="R17" t="n">
-        <v>7145628</v>
+        <v>7145336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,7 +2282,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128494305</v>
+        <v>128494312</v>
       </c>
       <c r="B18" t="n">
         <v>57689</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519885</v>
+        <v>520006</v>
       </c>
       <c r="R18" t="n">
-        <v>7145336</v>
+        <v>7145628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494324</v>
+        <v>128494332</v>
       </c>
       <c r="B21" t="n">
-        <v>80195</v>
+        <v>80194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519826</v>
+        <v>520316</v>
       </c>
       <c r="R21" t="n">
-        <v>7145720</v>
+        <v>7145323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128494332</v>
+        <v>128494324</v>
       </c>
       <c r="B22" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520316</v>
+        <v>519826</v>
       </c>
       <c r="R22" t="n">
-        <v>7145323</v>
+        <v>7145720</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -2180,7 +2180,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128494305</v>
+        <v>128494312</v>
       </c>
       <c r="B17" t="n">
         <v>57689</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519885</v>
+        <v>520006</v>
       </c>
       <c r="R17" t="n">
-        <v>7145336</v>
+        <v>7145628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,7 +2282,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128494312</v>
+        <v>128494305</v>
       </c>
       <c r="B18" t="n">
         <v>57689</v>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520006</v>
+        <v>519885</v>
       </c>
       <c r="R18" t="n">
-        <v>7145628</v>
+        <v>7145336</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,32 +2588,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494332</v>
+        <v>128494328</v>
       </c>
       <c r="B21" t="n">
-        <v>80194</v>
+        <v>97468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520316</v>
+        <v>520407</v>
       </c>
       <c r="R21" t="n">
-        <v>7145323</v>
+        <v>7145701</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128494324</v>
+        <v>128494332</v>
       </c>
       <c r="B22" t="n">
-        <v>80195</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519826</v>
+        <v>520316</v>
       </c>
       <c r="R22" t="n">
-        <v>7145720</v>
+        <v>7145323</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,32 +2782,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128494328</v>
+        <v>128494324</v>
       </c>
       <c r="B23" t="n">
-        <v>97468</v>
+        <v>80195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520407</v>
+        <v>519826</v>
       </c>
       <c r="R23" t="n">
-        <v>7145701</v>
+        <v>7145720</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128494325</v>
+        <v>128494315</v>
       </c>
       <c r="B4" t="n">
-        <v>80195</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519838</v>
+        <v>520004</v>
       </c>
       <c r="R4" t="n">
-        <v>7145721</v>
+        <v>7145622</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128494315</v>
+        <v>128494311</v>
       </c>
       <c r="B5" t="n">
         <v>57689</v>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520004</v>
+        <v>520007</v>
       </c>
       <c r="R5" t="n">
-        <v>7145622</v>
+        <v>7145630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494311</v>
+        <v>128494313</v>
       </c>
       <c r="B6" t="n">
         <v>57689</v>
@@ -1111,7 +1116,7 @@
         <v>520007</v>
       </c>
       <c r="R6" t="n">
-        <v>7145630</v>
+        <v>7145627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494313</v>
+        <v>128494325</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>80195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520007</v>
+        <v>519838</v>
       </c>
       <c r="R7" t="n">
-        <v>7145627</v>
+        <v>7145721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2588,32 +2588,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494328</v>
+        <v>128494324</v>
       </c>
       <c r="B21" t="n">
-        <v>97468</v>
+        <v>80195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520407</v>
+        <v>519826</v>
       </c>
       <c r="R21" t="n">
-        <v>7145701</v>
+        <v>7145720</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2782,32 +2782,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128494324</v>
+        <v>128494328</v>
       </c>
       <c r="B23" t="n">
-        <v>80195</v>
+        <v>97469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519826</v>
+        <v>520407</v>
       </c>
       <c r="R23" t="n">
-        <v>7145720</v>
+        <v>7145701</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128494331</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128494318</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128494315</v>
+        <v>128494325</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>80222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520004</v>
+        <v>519838</v>
       </c>
       <c r="R4" t="n">
-        <v>7145622</v>
+        <v>7145721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128494311</v>
+        <v>128494315</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520007</v>
+        <v>520004</v>
       </c>
       <c r="R5" t="n">
-        <v>7145630</v>
+        <v>7145622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494313</v>
+        <v>128494311</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,7 +1111,7 @@
         <v>520007</v>
       </c>
       <c r="R6" t="n">
-        <v>7145627</v>
+        <v>7145630</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494325</v>
+        <v>128494313</v>
       </c>
       <c r="B7" t="n">
-        <v>80195</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519838</v>
+        <v>520007</v>
       </c>
       <c r="R7" t="n">
-        <v>7145721</v>
+        <v>7145627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494327</v>
+        <v>128494307</v>
       </c>
       <c r="B8" t="n">
-        <v>80195</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520435</v>
+        <v>520304</v>
       </c>
       <c r="R8" t="n">
-        <v>7145468</v>
+        <v>7145224</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1348,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,27 +1379,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494333</v>
+        <v>128494317</v>
       </c>
       <c r="B9" t="n">
-        <v>57793</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1409,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520038</v>
+        <v>520006</v>
       </c>
       <c r="R9" t="n">
-        <v>7145570</v>
+        <v>7145617</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1450,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494330</v>
+        <v>128494314</v>
       </c>
       <c r="B10" t="n">
-        <v>80194</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519865</v>
+        <v>520005</v>
       </c>
       <c r="R10" t="n">
-        <v>7145612</v>
+        <v>7145625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1552,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494307</v>
+        <v>128494327</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>80222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520304</v>
+        <v>520435</v>
       </c>
       <c r="R11" t="n">
-        <v>7145224</v>
+        <v>7145468</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1639,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494317</v>
+        <v>128494330</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520006</v>
+        <v>519865</v>
       </c>
       <c r="R12" t="n">
-        <v>7145617</v>
+        <v>7145612</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,27 +1777,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494314</v>
+        <v>128494333</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>57820</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1807,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520005</v>
+        <v>520038</v>
       </c>
       <c r="R13" t="n">
-        <v>7145625</v>
+        <v>7145570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,11 +1848,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128494322</v>
+        <v>128494316</v>
       </c>
       <c r="B14" t="n">
-        <v>57686</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,16 +1885,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520419</v>
+        <v>520004</v>
       </c>
       <c r="R14" t="n">
-        <v>7145725</v>
+        <v>7145617</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128494316</v>
+        <v>128494310</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>520004</v>
       </c>
       <c r="R15" t="n">
-        <v>7145617</v>
+        <v>7145632</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128494310</v>
+        <v>128494322</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>57713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520004</v>
+        <v>520419</v>
       </c>
       <c r="R16" t="n">
-        <v>7145632</v>
+        <v>7145725</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2183,7 +2183,7 @@
         <v>128494312</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128494305</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>128494319</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>128494308</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,32 +2588,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494324</v>
+        <v>128494328</v>
       </c>
       <c r="B21" t="n">
-        <v>80195</v>
+        <v>97496</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519826</v>
+        <v>520407</v>
       </c>
       <c r="R21" t="n">
-        <v>7145720</v>
+        <v>7145701</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128494332</v>
+        <v>128494324</v>
       </c>
       <c r="B22" t="n">
-        <v>80194</v>
+        <v>80222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520316</v>
+        <v>519826</v>
       </c>
       <c r="R22" t="n">
-        <v>7145323</v>
+        <v>7145720</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,32 +2782,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128494328</v>
+        <v>128494332</v>
       </c>
       <c r="B23" t="n">
-        <v>97469</v>
+        <v>80221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520407</v>
+        <v>520316</v>
       </c>
       <c r="R23" t="n">
-        <v>7145701</v>
+        <v>7145323</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
         <v>128494309</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>128494320</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>128494323</v>
       </c>
       <c r="B26" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>128494321</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -1277,27 +1277,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494307</v>
+        <v>128494333</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>57820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520304</v>
+        <v>520038</v>
       </c>
       <c r="R8" t="n">
-        <v>7145224</v>
+        <v>7145570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494317</v>
+        <v>128494327</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>80222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520006</v>
+        <v>520435</v>
       </c>
       <c r="R9" t="n">
-        <v>7145617</v>
+        <v>7145468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1450,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494314</v>
+        <v>128494330</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520005</v>
+        <v>519865</v>
       </c>
       <c r="R10" t="n">
-        <v>7145625</v>
+        <v>7145612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494327</v>
+        <v>128494307</v>
       </c>
       <c r="B11" t="n">
-        <v>80222</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520435</v>
+        <v>520304</v>
       </c>
       <c r="R11" t="n">
-        <v>7145468</v>
+        <v>7145224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1639,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494330</v>
+        <v>128494317</v>
       </c>
       <c r="B12" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519865</v>
+        <v>520006</v>
       </c>
       <c r="R12" t="n">
-        <v>7145612</v>
+        <v>7145617</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1741,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,27 +1772,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494333</v>
+        <v>128494314</v>
       </c>
       <c r="B13" t="n">
-        <v>57820</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1812,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520038</v>
+        <v>520005</v>
       </c>
       <c r="R13" t="n">
-        <v>7145570</v>
+        <v>7145625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,6 +1843,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 34646-2025 artfynd.xlsx
+++ b/artfynd/A 34646-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128494331</v>
       </c>
       <c r="B2" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128494325</v>
+        <v>128494315</v>
       </c>
       <c r="B4" t="n">
-        <v>80222</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519838</v>
+        <v>520004</v>
       </c>
       <c r="R4" t="n">
-        <v>7145721</v>
+        <v>7145622</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128494315</v>
+        <v>128494311</v>
       </c>
       <c r="B5" t="n">
         <v>57716</v>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520004</v>
+        <v>520007</v>
       </c>
       <c r="R5" t="n">
-        <v>7145622</v>
+        <v>7145630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494311</v>
+        <v>128494313</v>
       </c>
       <c r="B6" t="n">
         <v>57716</v>
@@ -1111,7 +1116,7 @@
         <v>520007</v>
       </c>
       <c r="R6" t="n">
-        <v>7145630</v>
+        <v>7145627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494313</v>
+        <v>128494325</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>80226</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520007</v>
+        <v>519838</v>
       </c>
       <c r="R7" t="n">
-        <v>7145627</v>
+        <v>7145721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494333</v>
+        <v>128494327</v>
       </c>
       <c r="B8" t="n">
-        <v>57820</v>
+        <v>80226</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520038</v>
+        <v>520435</v>
       </c>
       <c r="R8" t="n">
-        <v>7145570</v>
+        <v>7145468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494327</v>
+        <v>128494307</v>
       </c>
       <c r="B9" t="n">
-        <v>80222</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520435</v>
+        <v>520304</v>
       </c>
       <c r="R9" t="n">
-        <v>7145468</v>
+        <v>7145224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1445,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494330</v>
+        <v>128494317</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519865</v>
+        <v>520006</v>
       </c>
       <c r="R10" t="n">
-        <v>7145612</v>
+        <v>7145617</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494307</v>
+        <v>128494314</v>
       </c>
       <c r="B11" t="n">
         <v>57716</v>
@@ -1603,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520304</v>
+        <v>520005</v>
       </c>
       <c r="R11" t="n">
-        <v>7145224</v>
+        <v>7145625</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494317</v>
+        <v>128494330</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>80225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1691,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520006</v>
+        <v>519865</v>
       </c>
       <c r="R12" t="n">
-        <v>7145617</v>
+        <v>7145612</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,27 +1777,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494314</v>
+        <v>128494333</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57820</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1807,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520005</v>
+        <v>520038</v>
       </c>
       <c r="R13" t="n">
-        <v>7145625</v>
+        <v>7145570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,11 +1848,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128494316</v>
+        <v>128494322</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,16 +1885,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520004</v>
+        <v>520419</v>
       </c>
       <c r="R14" t="n">
-        <v>7145617</v>
+        <v>7145725</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,7 +1976,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128494310</v>
+        <v>128494316</v>
       </c>
       <c r="B15" t="n">
         <v>57716</v>
@@ -2014,7 +2014,7 @@
         <v>520004</v>
       </c>
       <c r="R15" t="n">
-        <v>7145632</v>
+        <v>7145617</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128494322</v>
+        <v>128494310</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520419</v>
+        <v>520004</v>
       </c>
       <c r="R16" t="n">
-        <v>7145725</v>
+        <v>7145632</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2588,32 +2588,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494328</v>
+        <v>128494332</v>
       </c>
       <c r="B21" t="n">
-        <v>97496</v>
+        <v>80225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520407</v>
+        <v>520316</v>
       </c>
       <c r="R21" t="n">
-        <v>7145701</v>
+        <v>7145323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
         <v>128494324</v>
       </c>
       <c r="B22" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2782,32 +2782,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128494332</v>
+        <v>128494328</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>97502</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520316</v>
+        <v>520407</v>
       </c>
       <c r="R23" t="n">
-        <v>7145323</v>
+        <v>7145701</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
